--- a/data/trans_orig/P6715-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6715-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen sentido sus tareas del trabajo en 2012</t>
+          <t>Población según si tienen sentido sus tareas del trabajo en 2012 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>963</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>12042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>20409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16496</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30634</t>
+          <t>31802</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>15375</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32033</t>
+          <t>32113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>28042</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>32378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>55887</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34893</t>
+          <t>34766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53614</t>
+          <t>54084</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44852</t>
+          <t>43529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61772</t>
+          <t>60993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85686</t>
+          <t>85040</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111545</t>
+          <t>109916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>64,78%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19782</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26040</t>
+          <t>28400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32483</t>
+          <t>32901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56696</t>
+          <t>59654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>33866</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59002</t>
+          <t>59462</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73022</t>
+          <t>73015</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>107530</t>
+          <t>109654</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64862</t>
+          <t>65448</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96181</t>
+          <t>98123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51500</t>
+          <t>50239</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79392</t>
+          <t>77383</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123835</t>
+          <t>124031</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165919</t>
+          <t>167343</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>229094</t>
+          <t>225738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>266221</t>
+          <t>265403</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141779</t>
+          <t>142010</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175630</t>
+          <t>174074</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380654</t>
+          <t>378285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>430677</t>
+          <t>428457</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7435</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>16702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23873</t>
+          <t>25122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45897</t>
+          <t>45699</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74608</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>29646</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53777</t>
+          <t>55803</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>80661</t>
+          <t>83544</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120485</t>
+          <t>121900</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78053</t>
+          <t>79987</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>114537</t>
+          <t>112893</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53512</t>
+          <t>53960</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81573</t>
+          <t>82683</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139715</t>
+          <t>141130</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>185506</t>
+          <t>186325</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>241444</t>
+          <t>242691</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283011</t>
+          <t>281028</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>150095</t>
+          <t>149114</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184021</t>
+          <t>183111</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>402738</t>
+          <t>400869</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>454929</t>
+          <t>455063</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,0%</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20820</t>
+          <t>20072</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42277</t>
+          <t>42770</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21016</t>
+          <t>19830</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43889</t>
+          <t>42705</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47479</t>
+          <t>45827</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>77984</t>
+          <t>78208</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>69125</t>
+          <t>67632</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102727</t>
+          <t>103320</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37981</t>
+          <t>38165</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65735</t>
+          <t>66217</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>114468</t>
+          <t>115158</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>159440</t>
+          <t>158743</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>231218</t>
+          <t>228885</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>268751</t>
+          <t>267342</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119816</t>
+          <t>120903</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152292</t>
+          <t>152342</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>361204</t>
+          <t>359292</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>412889</t>
+          <t>410750</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -3459,97 +3459,97 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>2065</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,62 +3607,62 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>5496</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>4253</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>28782</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>22562</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45473</t>
+          <t>45102</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19943</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>40577</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21600</t>
+          <t>22016</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32230</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>56723</t>
+          <t>56157</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>94980</t>
+          <t>97102</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>119874</t>
+          <t>119951</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>33452</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50346</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>134269</t>
+          <t>134234</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>165192</t>
+          <t>163282</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -4141,97 +4141,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4367,97 +4367,97 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4480,97 +4480,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>14569</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>33731</t>
+          <t>34146</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>32131</t>
+          <t>32411</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>31570</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t>57400</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>140828</t>
+          <t>140832</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>190083</t>
+          <t>187550</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>120821</t>
+          <t>119466</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>165256</t>
+          <t>165605</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>271669</t>
+          <t>270698</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>336278</t>
+          <t>338308</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>280558</t>
+          <t>282577</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>346860</t>
+          <t>346216</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>188506</t>
+          <t>190680</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>242265</t>
+          <t>245139</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>483928</t>
+          <t>490877</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>565719</t>
+          <t>568812</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>877969</t>
+          <t>878206</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>951783</t>
+          <t>949987</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>528804</t>
+          <t>524803</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>592315</t>
+          <t>591828</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1429012</t>
+          <t>1428185</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1531251</t>
+          <t>1523844</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen sentido sus tareas del trabajo en 2016</t>
+          <t>Población según si tienen sentido sus tareas del trabajo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6422,97 +6422,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1085</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4755</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4478</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5428</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11385</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22839</t>
+          <t>23942</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>30194</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26629</t>
+          <t>25747</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49585</t>
+          <t>48487</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17371</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34128</t>
+          <t>33074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>18204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34605</t>
+          <t>35252</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>40228</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65513</t>
+          <t>64705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>28280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47201</t>
+          <t>45914</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30424</t>
+          <t>31638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49105</t>
+          <t>50283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63999</t>
+          <t>64727</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90729</t>
+          <t>90717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>17096</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26282</t>
+          <t>26613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16163</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35700</t>
+          <t>36471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46235</t>
+          <t>46025</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74782</t>
+          <t>76326</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30458</t>
+          <t>30668</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53684</t>
+          <t>54124</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84051</t>
+          <t>84881</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>121542</t>
+          <t>121923</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90534</t>
+          <t>90682</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125572</t>
+          <t>124419</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68399</t>
+          <t>68710</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97591</t>
+          <t>96846</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167632</t>
+          <t>169201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212820</t>
+          <t>211919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135407</t>
+          <t>137068</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173363</t>
+          <t>174286</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122731</t>
+          <t>121874</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153981</t>
+          <t>155660</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>268215</t>
+          <t>267669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315287</t>
+          <t>316526</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,23%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19153</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24830</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19019</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>18995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48235</t>
+          <t>49290</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79827</t>
+          <t>78910</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28413</t>
+          <t>28306</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51941</t>
+          <t>51098</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>85377</t>
+          <t>84504</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124304</t>
+          <t>122411</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110058</t>
+          <t>111785</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>151044</t>
+          <t>150307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67614</t>
+          <t>67847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>97561</t>
+          <t>98377</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>189507</t>
+          <t>187794</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>237393</t>
+          <t>237307</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222343</t>
+          <t>225268</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265407</t>
+          <t>266180</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>163144</t>
+          <t>162194</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>199520</t>
+          <t>198072</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>397877</t>
+          <t>398274</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>451237</t>
+          <t>452936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,29%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14316</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21379</t>
+          <t>21763</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22602</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>16695</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33082</t>
+          <t>33476</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35735</t>
+          <t>35200</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60978</t>
+          <t>60465</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>27477</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48393</t>
+          <t>49709</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>66460</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>101615</t>
+          <t>100737</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87986</t>
+          <t>85476</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>122682</t>
+          <t>121258</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52152</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81621</t>
+          <t>81252</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148871</t>
+          <t>146937</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>193444</t>
+          <t>195656</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>177416</t>
+          <t>178380</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>216905</t>
+          <t>218554</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>109788</t>
+          <t>110524</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>142927</t>
+          <t>141641</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>294995</t>
+          <t>297250</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>347322</t>
+          <t>348029</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>21263</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40155</t>
+          <t>40475</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30575</t>
+          <t>30782</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>35258</t>
+          <t>37193</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>64338</t>
+          <t>63451</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26824</t>
+          <t>27521</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>48860</t>
+          <t>49596</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>22112</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>41230</t>
+          <t>42125</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>53246</t>
+          <t>52926</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>84279</t>
+          <t>83721</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>75016</t>
+          <t>75787</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>101994</t>
+          <t>102004</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>36358</t>
+          <t>36488</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>58638</t>
+          <t>59187</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>118584</t>
+          <t>118589</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>154423</t>
+          <t>154115</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,74%</t>
         </is>
       </c>
     </row>
@@ -9832,97 +9832,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9945,97 +9945,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10093,62 +10093,62 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>10,12%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -10206,62 +10206,62 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>4223</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>4265</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -10514,97 +10514,97 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10627,97 +10627,97 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10740,97 +10740,97 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10853,97 +10853,97 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10966,97 +10966,97 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
           <t>795</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>26256</t>
+          <t>25272</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>54204</t>
+          <t>54310</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>40101</t>
+          <t>41488</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>71694</t>
+          <t>71835</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>26195</t>
+          <t>25640</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>49142</t>
+          <t>49270</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>73917</t>
+          <t>73620</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>115847</t>
+          <t>109854</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>187394</t>
+          <t>185269</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>245956</t>
+          <t>243199</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>136914</t>
+          <t>138073</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>184754</t>
+          <t>184299</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>338013</t>
+          <t>336138</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>408699</t>
+          <t>408330</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>365035</t>
+          <t>370270</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>439389</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>259519</t>
+          <t>261970</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>316957</t>
+          <t>321751</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>643117</t>
+          <t>646749</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>735226</t>
+          <t>739985</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>689035</t>
+          <t>687163</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>765355</t>
+          <t>763921</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>507967</t>
+          <t>501356</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>571463</t>
+          <t>564509</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1213632</t>
+          <t>1209858</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1310511</t>
+          <t>1312738</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6715-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6715-Edad-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12042</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>19507</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31802</t>
+          <t>31156</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15375</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32113</t>
+          <t>31747</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28042</t>
+          <t>27871</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32378</t>
+          <t>31980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55887</t>
+          <t>54982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34766</t>
+          <t>35537</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54084</t>
+          <t>53678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43529</t>
+          <t>43575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60993</t>
+          <t>61870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85040</t>
+          <t>85930</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109916</t>
+          <t>111938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,97%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>19454</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>9550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28400</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32901</t>
+          <t>32661</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59654</t>
+          <t>58601</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33866</t>
+          <t>34540</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59462</t>
+          <t>58794</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73015</t>
+          <t>71220</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109654</t>
+          <t>107803</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65448</t>
+          <t>65692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98123</t>
+          <t>96810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50239</t>
+          <t>50899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77383</t>
+          <t>78863</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124031</t>
+          <t>124100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167343</t>
+          <t>169103</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225738</t>
+          <t>225496</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265403</t>
+          <t>264010</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142010</t>
+          <t>141279</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174074</t>
+          <t>174677</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378285</t>
+          <t>380412</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>428457</t>
+          <t>429616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,13%</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15193</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25122</t>
+          <t>24444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45699</t>
+          <t>45313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74125</t>
+          <t>74192</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29646</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55803</t>
+          <t>55428</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83544</t>
+          <t>82411</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>121900</t>
+          <t>120815</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79987</t>
+          <t>77908</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112893</t>
+          <t>112944</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53960</t>
+          <t>53108</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82683</t>
+          <t>81858</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141130</t>
+          <t>140723</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>186325</t>
+          <t>186225</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>242691</t>
+          <t>243430</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281028</t>
+          <t>282616</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>149114</t>
+          <t>150485</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>183111</t>
+          <t>182203</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>400869</t>
+          <t>400385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>455063</t>
+          <t>455847</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,11%</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20072</t>
+          <t>20235</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42770</t>
+          <t>41936</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19830</t>
+          <t>20950</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42705</t>
+          <t>41923</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45827</t>
+          <t>46909</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78208</t>
+          <t>77764</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67632</t>
+          <t>68710</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103320</t>
+          <t>104319</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38165</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66217</t>
+          <t>66170</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>115158</t>
+          <t>115256</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>158743</t>
+          <t>160097</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>228885</t>
+          <t>230381</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>267342</t>
+          <t>268574</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>120903</t>
+          <t>122742</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152342</t>
+          <t>152387</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>359292</t>
+          <t>360688</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>410750</t>
+          <t>410433</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28782</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21752</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>22853</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45102</t>
+          <t>45518</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20203</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40577</t>
+          <t>41301</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>21353</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32517</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>56157</t>
+          <t>55272</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>97102</t>
+          <t>95854</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>119951</t>
+          <t>120154</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>33452</t>
+          <t>33294</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>50340</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>134234</t>
+          <t>134555</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>163282</t>
+          <t>165393</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,77 +5525,77 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>6176</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>13422</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>12425</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>7044</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>21531</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>6176</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>2871</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>12849</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>12425</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>6761</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>20739</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>33757</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>32308</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>57400</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>140832</t>
+          <t>140876</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>187550</t>
+          <t>189782</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>119466</t>
+          <t>118568</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>165605</t>
+          <t>165440</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>270698</t>
+          <t>271083</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>338308</t>
+          <t>337885</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>282577</t>
+          <t>282984</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>346216</t>
+          <t>347676</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>190680</t>
+          <t>188304</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>245139</t>
+          <t>245949</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>490877</t>
+          <t>487004</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>568812</t>
+          <t>571375</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>878206</t>
+          <t>878454</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>949987</t>
+          <t>951657</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>524803</t>
+          <t>528088</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>591828</t>
+          <t>591976</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1428185</t>
+          <t>1424726</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1523844</t>
+          <t>1524689</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11548</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23942</t>
+          <t>23420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14351</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30194</t>
+          <t>30183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>26003</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48487</t>
+          <t>47025</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16756</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33074</t>
+          <t>34318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18204</t>
+          <t>19069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35252</t>
+          <t>35684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40228</t>
+          <t>40352</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64705</t>
+          <t>64878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>27423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45914</t>
+          <t>45421</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31638</t>
+          <t>30733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50283</t>
+          <t>49510</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>64483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90717</t>
+          <t>90280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10496</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26613</t>
+          <t>26454</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>36718</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46025</t>
+          <t>47156</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76326</t>
+          <t>76822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>31720</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54124</t>
+          <t>54522</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84881</t>
+          <t>82301</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>121923</t>
+          <t>121766</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90682</t>
+          <t>89348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124419</t>
+          <t>123284</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68710</t>
+          <t>69847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96846</t>
+          <t>99483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169201</t>
+          <t>168004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211919</t>
+          <t>210460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137068</t>
+          <t>136360</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174286</t>
+          <t>173078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121874</t>
+          <t>121284</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155660</t>
+          <t>152933</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>267669</t>
+          <t>268104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>316526</t>
+          <t>316177</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18276</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21357</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18995</t>
+          <t>17545</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>37620</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49290</t>
+          <t>49191</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78910</t>
+          <t>80604</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28306</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51098</t>
+          <t>51384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84504</t>
+          <t>83920</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>122411</t>
+          <t>125527</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111785</t>
+          <t>108687</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>150307</t>
+          <t>150873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67847</t>
+          <t>68360</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98377</t>
+          <t>98506</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>187794</t>
+          <t>188738</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>237307</t>
+          <t>239703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225268</t>
+          <t>225041</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266180</t>
+          <t>269226</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>162194</t>
+          <t>162734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>198072</t>
+          <t>195592</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>398274</t>
+          <t>398724</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>452936</t>
+          <t>454763</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21763</t>
+          <t>22164</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22781</t>
+          <t>23837</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>13067</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33476</t>
+          <t>33295</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35200</t>
+          <t>34413</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60465</t>
+          <t>61664</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27477</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49709</t>
+          <t>49068</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>66460</t>
+          <t>66597</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>100737</t>
+          <t>103141</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85476</t>
+          <t>86377</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>121258</t>
+          <t>121102</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51889</t>
+          <t>51631</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81252</t>
+          <t>84287</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>146937</t>
+          <t>146636</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195656</t>
+          <t>190146</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>178380</t>
+          <t>177255</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>218554</t>
+          <t>215828</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110524</t>
+          <t>108824</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>141641</t>
+          <t>141972</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>297250</t>
+          <t>297826</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>348029</t>
+          <t>352383</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>11026</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21263</t>
+          <t>21153</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40475</t>
+          <t>39424</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12435</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30782</t>
+          <t>30155</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37193</t>
+          <t>36727</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>63451</t>
+          <t>64600</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27521</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>49596</t>
+          <t>49571</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>22299</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>42125</t>
+          <t>41329</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52926</t>
+          <t>54157</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>83721</t>
+          <t>85259</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>75787</t>
+          <t>75125</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>102004</t>
+          <t>101285</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>36488</t>
+          <t>37330</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>59187</t>
+          <t>58613</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>118589</t>
+          <t>118720</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>154115</t>
+          <t>154366</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>35524</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,49 +11211,49 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>16260</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>25899</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>16260</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>9272</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>25272</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>37</t>
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>28081</t>
+          <t>28011</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>54310</t>
+          <t>53802</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>41488</t>
+          <t>41094</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>71835</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>25640</t>
+          <t>25335</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>49270</t>
+          <t>49680</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>73620</t>
+          <t>72782</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>113345</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>185269</t>
+          <t>186250</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>243199</t>
+          <t>244042</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>138073</t>
+          <t>137120</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>184299</t>
+          <t>184029</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>336138</t>
+          <t>339761</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>408330</t>
+          <t>414218</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>370270</t>
+          <t>367716</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>438466</t>
+          <t>436226</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,49 +11550,49 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
+          <t>30,67%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>288412</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>262100</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>319738</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>27,81%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>25,27%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
           <t>30,83%</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>288412</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>261970</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>321751</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>27,81%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>25,26%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>31,02%</t>
-        </is>
-      </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>668</t>
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>646749</t>
+          <t>645287</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>739985</t>
+          <t>735483</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>687163</t>
+          <t>690276</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>763921</t>
+          <t>766886</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>501356</t>
+          <t>504407</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>564509</t>
+          <t>570991</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1209858</t>
+          <t>1212019</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1312738</t>
+          <t>1312523</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
